--- a/reports/obex/2026-06/obex_settlement_june_2026.xlsx
+++ b/reports/obex/2026-06/obex_settlement_june_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2412429.288510267</v>
+        <v>2422417.555340011</v>
       </c>
     </row>
     <row r="5">
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>69775.64596112848</v>
+        <v>67174.42411902001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>2482204.934471395</v>
+        <v>2489591.979459031</v>
       </c>
     </row>
     <row r="8">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="18">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>2412429.288510267</v>
+        <v>2422417.555340011</v>
       </c>
     </row>
     <row r="20">
@@ -611,13 +611,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-1997989.049948277</v>
+        <v>-1925370.687968509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" s="4" t="n">
-        <v>414440.2385619898</v>
+        <v>497046.8673715019</v>
       </c>
     </row>
     <row r="23">
@@ -640,7 +640,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ethereum=25433093</t>
+          <t>ethereum=25433938</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-03T07:05:53+00:00</t>
+          <t>2026-07-15T11:28:21+00:00</t>
         </is>
       </c>
     </row>
@@ -825,19 +825,19 @@
         <v>613361592.2739345</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>615774021.5624447</v>
+        <v>615784009.8292744</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>2412429.288510267</v>
+        <v>2422417.555340011</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>2412429.288510267</v>
+        <v>2422417.555340011</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>2412429.288510267</v>
+        <v>2422417.555340011</v>
       </c>
       <c r="K2" s="5" t="n">
         <v>0</v>
@@ -849,13 +849,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
       <c r="O2" s="5" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
       <c r="P2" s="5" t="n">
-        <v>414440.2385619898</v>
+        <v>497046.8673715019</v>
       </c>
       <c r="Q2" s="5" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="5">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="8">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="11">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
     <row r="12">
@@ -1199,16 +1199,16 @@
         <v>609858163</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="7">
@@ -1239,16 +1239,16 @@
         <v>609858163</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="8">
@@ -1279,16 +1279,16 @@
         <v>609858163</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="9">
@@ -1319,16 +1319,16 @@
         <v>609858163</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="10">
@@ -1359,16 +1359,16 @@
         <v>609858163</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="11">
@@ -1399,16 +1399,16 @@
         <v>609858163</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="12">
@@ -1439,16 +1439,16 @@
         <v>609858163</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="13">
@@ -1479,16 +1479,16 @@
         <v>609858163</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="14">
@@ -1519,16 +1519,16 @@
         <v>609858163</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="15">
@@ -1559,16 +1559,16 @@
         <v>609858163</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="16">
@@ -1599,16 +1599,16 @@
         <v>609858163</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="17">
@@ -1639,16 +1639,16 @@
         <v>609858163</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="18">
@@ -1679,16 +1679,16 @@
         <v>609858163</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="19">
@@ -1719,16 +1719,16 @@
         <v>609858163</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="20">
@@ -1759,16 +1759,16 @@
         <v>609858163</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="21">
@@ -1799,16 +1799,16 @@
         <v>609858163</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="22">
@@ -1839,16 +1839,16 @@
         <v>609858163</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="23">
@@ -1879,16 +1879,16 @@
         <v>609858163</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="24">
@@ -1919,16 +1919,16 @@
         <v>609858163</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="25">
@@ -1959,16 +1959,16 @@
         <v>609858163</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="26">
@@ -1999,16 +1999,16 @@
         <v>609858163</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>66519.07872897816</v>
+        <v>64101.39453905395</v>
       </c>
     </row>
     <row r="27">
@@ -2039,16 +2039,16 @@
         <v>612320008</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="28">
@@ -2079,16 +2079,16 @@
         <v>612320008</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="29">
@@ -2119,16 +2119,16 @@
         <v>612320008</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="30">
@@ -2159,16 +2159,16 @@
         <v>612320008</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="31">
@@ -2199,16 +2199,16 @@
         <v>612320008</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="32">
@@ -2239,16 +2239,16 @@
         <v>612320008</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="33">
@@ -2279,16 +2279,16 @@
         <v>612320008</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="34">
@@ -2319,16 +2319,16 @@
         <v>612320008</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="35">
@@ -2359,16 +2359,16 @@
         <v>612320008</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>0.03750000355548933</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.04061250356615579</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>66787.59962663734</v>
+        <v>64360.15584981957</v>
       </c>
     </row>
     <row r="37">
@@ -2387,10 +2387,10 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" s="10" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>1997989.049948277</v>
+        <v>1925370.687968509</v>
       </c>
     </row>
   </sheetData>
